--- a/SWOT_Higienizado.xlsx
+++ b/SWOT_Higienizado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,18 +453,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Metodologia estruturada e padronizada</t>
+          <t>Equipe técnica qualificada e expertise consolidada</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>18.5</v>
+        <v>24.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A metodologia desenvolvida (canvas, plano de trabalho...) ||| Aplicação de metodologias de gestão de processos ||| Atuar com metodologia clara ||| Base metodológica robusta e em contínua melhoria ||| Centralização Metodológica - Padronização e consistência ||| Construção da gestão por processos, com foco em melhoria contínua, padronização e eficiência organizacional. ||| Disponibilização de Guias Técnicos e treinamento dos especialistas em processo alocados nos Nuproc’s ||| Dispõe de guias, modelos, fluxos e ferramentas estruturadas ||| Equipe técnica estruturada e com conhecimento em metodologias de gestão por processos, contribuindo para a padronização das atividades e a melhoria continua dos serviços ||| Existência de metodologias de trabalho ||| Forte alinhamento metodológico ||| Metodologia ||| Metodologia BPM ||| Metodologia Estruturada: Utiliza um framework de melhoria baseado no padrão internacional BPM CBOK, garantindo rigor técnico e padronização ||| Metodologia consolidada ||| Metodologia e instrumentos padronizados ||| Metodologia estruturada ||| Metodologia padronizada ||| Metodologia para o plano de trabalho ||| Metodologia sólida e bem estruturada. ||| Nossa principal força institucional é a metodologia desenvolvida e aplicada pelo EPROC, que confere padronização, eficiência e qualidade às entregas, além de fortalecer a gestão por processos no órgão. ||| O EPROC possui equipe com conhecimento técnico consolidado em gestão por processos, metodologias de mapeamento e melhoria contínua. Essa capacidade interna assegura qualidade nas entregas, consistência metodológica e maior efetividade nas iniciativas conduzidas. ||| O setor dispõe de metodologia definida para condução dos trabalhos de mapeamento, análise e redesenho de processos, o que garante padronização, organização e rastreabilidade das atividades. Essa estrutura favorece a replicação das práticas e a evolução da maturidade em gestão por processos. ||| Organização e padronização dos processos ||| Padronização ||| Padronização: o núcleo garante consistência e alinhamento estratégico nas iniciativas de processos em todos os órgãos ||| Procedimentos normativos de fácil acesso ||| Uso de metodologias e ferramentas de gestão de processos ||| metodologia ||| metodologia padronizada</t>
+          <t>A modalidade de contratação de especialistas permite um corpo técnico capacitado, escolhido e selecionado dentro de critérios rígidos como experiência, capacidade técnica.  Conhecimentos multidiciplinares. ||| Alta capacidade intelectual ||| Capacidade Técnica do Time ||| Capacidade técnica ||| Capacidade técnica da equipe aliada ao conhecimento dos processos institucionais. ||| Capacidade técnica para planejar, monitorar, analisar e avaliar políticas públicas e a gestão estratégica do Estado. ||| Capacidade técnica qualificada da equipe, com conhecimento especializado em planejamento, gestão e análise de dados públicos. ||| Colaboradores altamente qualificados ||| Conhecimento ||| Conhecimento, organização, profissionais copetentes ||| Corpo técnico com anos de experiência em mapeamento ||| Domínio ||| Domínio técnico sobre o Programa de Incentivo à Cultura (PIC) e os Editais. ||| Equipe altamente capacitada e engajada ||| Equipe altamente qualificada. ||| Equipe diversificada-pessoas de áreas diferentes ||| Equipe engajada ||| Equipe grande ||| Equipe qualificada e multidisciplinar ||| Equipe qualificada e multidisciplinar, composta por especialistas com diferentes competências, atuando de forma colaborativa em prol de objetivos institucionais comuns. ||| Equipe técnica estruturada e com conhecimento em metodologias de gestão por processos, contribuindo para a padronização das atividades e a melhoria continua dos serviços ||| Equipe técnica qualificada ||| Equipe técnica qualificada e com conhecimento dos fluxos e sistemas institucionais. ||| Equipe técnica qualificada e comprometida ||| Equipe técnica qualificada, com conhecimento especializado nos processos e forte cultura de compartilhamento de conhecimento entre a equipe ||| Equipe técnica qualificada. ||| Equipes comprometidas. ||| Especialistas na área de processos com ampla bagagem profissional e acadêmica ||| Experiência consolidada ||| O EPROC conta com profissionais especializados em gestão de processos ||| O EPROC possui equipe com conhecimento técnico consolidado em gestão por processos, metodologias de mapeamento e melhoria contínua. Essa capacidade interna assegura qualidade nas entregas, consistência metodológica e maior efetividade nas iniciativas conduzidas. ||| Pessoas ||| Produção de conhecimento institucional ||| Servidores com profundo conhecimento na gestão de editais e fomento cultural. ||| Ter uma equipe multidisciplinar qualificada ||| Time experiente ||| capacidades/expertises ||| competencias ||| conhecimento ||| experiência</t>
         </is>
       </c>
     </row>
@@ -474,18 +474,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equipe técnica qualificada e multidisciplinar</t>
+          <t>Metodologia estruturada e padronizada</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>13.6</v>
+        <v>21</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alta capacidade intelectual ||| Capacidade Técnica do Time ||| Colaboradores altamente qualificados ||| Conhecimento, organização, profissionais copetentes ||| Corpo técnico com anos de experiência em mapeamento ||| Equipe altamente capacitada e engajada ||| Equipe altamente qualificada. ||| Equipe diversificada-pessoas de áreas diferentes ||| Equipe engajada ||| Equipe grande ||| Equipe qualificada e multidisciplinar ||| Equipe qualificada e multidisciplinar, composta por especialistas com diferentes competências, atuando de forma colaborativa em prol de objetivos institucionais comuns. ||| Equipe técnica qualificada ||| Equipe técnica qualificada e com conhecimento dos fluxos e sistemas institucionais. ||| Equipe técnica qualificada e comprometida ||| Equipe técnica qualificada, com conhecimento especializado nos processos e forte cultura de compartilhamento de conhecimento entre a equipe ||| Equipe técnica qualificada. ||| Equipes comprometidas. ||| Especialistas na área de processos com ampla bagagem profissional e acadêmica ||| O EPROC conta com profissionais especializados em gestão de processos ||| Ter uma equipe multidisciplinar qualificada ||| Time experiente</t>
+          <t>A metodologia desenvolvida (canvas, plano de trabalho...) ||| Aplicação de metodologias de gestão de processos ||| Atuar com metodologia clara ||| Atuação transversal, com potencial de alcançar diferentes áreas da administração pública e promover alinhamento entre gestão, planejamento e execução ||| Base metodológica robusta e em contínua melhoria ||| Capacidade de criar um "Guia de Processos" único para o Estado, garantindo que diferentes secretarias falem a mesma língua ||| Centralização Metodológica - Padronização e consistência ||| Construção da gestão por processos, com foco em melhoria contínua, padronização e eficiência organizacional. ||| Disponibilização de Guias Técnicos e treinamento dos especialistas em processo alocados nos Nuproc’s ||| Dispõe de guias, modelos, fluxos e ferramentas estruturadas ||| Elaboração do Planejamento Estratégico dos Nuproc’s pelo Eproc ||| Existência de metodologias de trabalho ||| Forte alinhamento metodológico ||| Integração institucional entre órgãos e áreas, com atuação em todo o ciclo de planejamento e gestão. ||| Metodologia ||| Metodologia BPM ||| Metodologia Estruturada: Utiliza um framework de melhoria baseado no padrão internacional BPM CBOK, garantindo rigor técnico e padronização ||| Metodologia consolidada ||| Metodologia e instrumentos padronizados ||| Metodologia estruturada ||| Metodologia padronizada ||| Metodologia para o plano de trabalho ||| Metodologia sólida e bem estruturada. ||| Nossa principal força institucional é a metodologia desenvolvida e aplicada pelo EPROC, que confere padronização, eficiência e qualidade às entregas, além de fortalecer a gestão por processos no órgão. ||| O setor dispõe de metodologia definida para condução dos trabalhos de mapeamento, análise e redesenho de processos, o que garante padronização, organização e rastreabilidade das atividades. Essa estrutura favorece a replicação das práticas e a evolução da maturidade em gestão por processos. ||| Organização e padronização dos processos ||| Orientação ||| Padronização ||| Padronização: o núcleo garante consistência e alinhamento estratégico nas iniciativas de processos em todos os órgãos ||| Planejamento ||| Procedimentos normativos de fácil acesso ||| Uso de metodologias e ferramentas de gestão de processos ||| metodologia ||| metodologia padronizada</t>
         </is>
       </c>
     </row>
@@ -495,18 +495,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Conhecimento técnico e expertise consolidada</t>
+          <t>Engajamento, comprometimento e cultura de integridade</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>9.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A modalidade de contratação de especialistas permite um corpo técnico capacitado, escolhido e selecionado dentro de critérios rígidos como experiência, capacidade técnica.  Conhecimentos multidiciplinares. ||| Capacidade técnica ||| Capacidade técnica da equipe aliada ao conhecimento dos processos institucionais. ||| Capacidade técnica para planejar, monitorar, analisar e avaliar políticas públicas e a gestão estratégica do Estado. ||| Capacidade técnica qualificada da equipe, com conhecimento especializado em planejamento, gestão e análise de dados públicos. ||| Conhecimento ||| Domínio ||| Domínio técnico sobre o Programa de Incentivo à Cultura (PIC) e os Editais. ||| Experiência consolidada ||| Produção de conhecimento institucional ||| Servidores com profundo conhecimento na gestão de editais e fomento cultural. ||| capacidades/expertises ||| competencias ||| conhecimento ||| experiência</t>
+          <t>Acolhedor ||| Adaptação e resiliência ||| Boa capacidade de adaptação e servidores comprometidos ||| Comprometimento da equipe com a qualidade das entregas e responsabilidade institucional. ||| Cultura institucional orientada a resultados, que promove o engajamento dos colaboradores e a resiliência diante de mudanças estruturais. ||| Determinação ||| Engajamento e comprometimento dos especialistas na construção de soluções que promovam uma Santa Catarina mais eficiente, inovadora e orientada ao cidadão. ||| Engajamento, trabalho  em equipe ||| Força é a firmeza em cumprir deveres com integridade. ||| Força é a união de propósito e disciplina que sustenta decisões corretas. ||| Força é agir com responsabilidade e coesão, garantindo que decisões difíceis sejam tomadas com justiça e foco no interesse público. ||| Governança de processos com papéis, responsabilidades e fluxos de aprovação definidos. Cultura de melhoria contínua com registro e compartilhamento de lições aprendidas. Infraestrutura tecnológica adequada para modelagem, análise e monitoramento de processos. Alinhamento das atividades do EPROC aos objetivos estratégicos da SEPLAN. ||| Profissionalismo ||| Resistência ||| Trabalho em equipe ||| acolhedor ||| comprometimento ||| evado grau de colaboração e trabalho em equipe intersetorial, facilitando a agilidade na resolução de problemas e o fluxo de demandas complexas.</t>
         </is>
       </c>
     </row>
@@ -516,18 +516,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Engajamento e comprometimento da equipe</t>
+          <t>Entrega de valor e alinhamento a políticas públicas</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Acolhedor ||| Adaptação e resiliência ||| Boa capacidade de adaptação e servidores comprometidos ||| Comprometimento da equipe com a qualidade das entregas e responsabilidade institucional. ||| Cultura institucional orientada a resultados, que promove o engajamento dos colaboradores e a resiliência diante de mudanças estruturais. ||| Determinação ||| Engajamento e comprometimento dos especialistas na construção de soluções que promovam uma Santa Catarina mais eficiente, inovadora e orientada ao cidadão. ||| Engajamento, trabalho  em equipe ||| Profissionalismo ||| Trabalho em equipe ||| acolhedor ||| comprometimento ||| evado grau de colaboração e trabalho em equipe intersetorial, facilitando a agilidade na resolução de problemas e o fluxo de demandas complexas.</t>
+          <t>A variedade de serviços permite ao EPROC apoiar cada órgão de acordo com sua necessidade.. ||| Agilidade na resposta a demandas estratégicas, com prazos cumpridos e qualidade técnica. Competência em traduzir necessidades institucionais em processos claros, eficientes e documentados. Capacidade de inovação na aplicação de ferramentas de gestão e tecnologias de suporte a processos. Comprometimento da equipe com resultados institucionais e com a melhoria do serviço público. ||| Ampla oferta de serviços integrados ||| Análise e sistematização de dados para suporte à tomada de decisão. ||| Controle ||| Disponibilidade e uso estratégico de informações e sistemas para apoio à tomada de decisão baseada em evidências. ||| Diversidade de carta de serviços ||| Diversidade de programas de incentivo ao esporte (PIDE, PIE, Bolsa Atleta) ||| Eficiência ||| Entrega de valor ao cidadão catarinense ||| Eventos com grande participação e qualidade na organização ||| Foco institucional no fortalecimento da agricultura familiar, alinhado às políticas públicas e à geração de valor para o setor agropecuário estadual. ||| O EPROC apresenta boa organização interna, com definição de fluxos de trabalho e alinhamento entre os membros da equipe. Isso contribui para maior eficiência operacional, melhor gestão das demandas e cumprimento dos objetivos estabelecidos. ||| Padronização e organização de processos, garantindo maior eficiência e qualidade nas entregas. ||| Produção de entregas estruturadas ||| Promove eventos para a prática esportiva em Santa Catarina, com diversidade e inclusão. ||| Proposta de valor clara e consistente ||| Utilização de ferramentas que garantem maior eficiência e controle das atividades.</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Entrega de valor e eficiência nos resultados</t>
+          <t>Melhoria contínua e inovação</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -548,7 +548,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A variedade de serviços permite ao EPROC apoiar cada órgão de acordo com sua necessidade.. ||| Ampla oferta de serviços integrados ||| Análise e sistematização de dados para suporte à tomada de decisão. ||| Controle ||| Diversidade de carta de serviços ||| Eficiência ||| Entrega de valor ao cidadão catarinense ||| Eventos com grande participação e qualidade na organização ||| O EPROC apresenta boa organização interna, com definição de fluxos de trabalho e alinhamento entre os membros da equipe. Isso contribui para maior eficiência operacional, melhor gestão das demandas e cumprimento dos objetivos estabelecidos. ||| Padronização e organização de processos, garantindo maior eficiência e qualidade nas entregas. ||| Produção de entregas estruturadas ||| Proposta de valor clara e consistente ||| Utilização de ferramentas que garantem maior eficiência e controle das atividades.</t>
+          <t>Capacidade de fomentar amadurecimento organizacional ||| Capacidade de promover melhorias contínuas e otimização de processos internos. ||| Criatividade ||| Inovação ||| Liderança na modernização da gestão pública ||| Medernização ||| Melhorias para as Instituições ||| Transformação ||| melhorias ||| potencial para inovar e crescer ||| rocessos estruturados e em constante aprimoramento</t>
         </is>
       </c>
     </row>
@@ -558,18 +558,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Não classificado (revisar manualmente)</t>
+          <t>Integração e articulação institucional</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Capacidade de criar um "Guia de Processos" único para o Estado, garantindo que diferentes secretarias falem a mesma língua ||| Condução bem definida na implantação da gestão por processos ||| Diversidade de programas de incentivo ao esporte (PIDE, PIE, Bolsa Atleta) ||| Foco institucional no fortalecimento da agricultura familiar, alinhado às políticas públicas e à geração de valor para o setor agropecuário estadual. ||| Força é a firmeza em cumprir deveres com integridade. ||| Força é a união de propósito e disciplina que sustenta decisões corretas. ||| Força é agir com responsabilidade e coesão, garantindo que decisões difíceis sejam tomadas com justiça e foco no interesse público. ||| Orientação ||| Pessoas ||| Planejamento ||| Promove eventos para a prática esportiva em Santa Catarina, com diversidade e inclusão. ||| Resistência ||| potencial para inovar e crescer</t>
+          <t>Atuação integrada com base em indicadores, dados e articulação intersetorial, fortalecendo a tomada de decisão ||| Equipe especializada em BPMN com capacidade de disseminação metodológica. Integração estratégica EPROC/SEPLAN/órgãos para alinhamento de prioridades e otimização de fluxos. Padronização de documentos e roteiros com rastreabilidade, qualidade. Experiência em modernização administrativa com entregas de ganhos de eficiência mensuráveis. Articulação interinstitucional para soluções transversais, reduzindo retrabalho. ||| Integração ||| Integração com órgãos parceiros. ||| Integração e cooperação entre os membros da equipe, favorecendo a fluidez dos processos e a resolutividade das demandas. ||| Integração institucional e articulação eficiente entre órgãos governamentais, facilitando a implementação de políticas públicas. ||| O escritório possui atuação junto a diferentes órgãos do governo, o que amplia sua visão sistêmica da administração pública e fortalece sua capacidade de integração, padronização e disseminação de boas práticas ||| conexões/interações ||| relações interpessoais</t>
         </is>
       </c>
     </row>
@@ -579,18 +579,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Melhoria contínua e inovação</t>
+          <t>Apoio da alta gestão e governança</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Capacidade de fomentar amadurecimento organizacional ||| Capacidade de promover melhorias contínuas e otimização de processos internos. ||| Criatividade ||| Inovação ||| Liderança na modernização da gestão pública ||| Medernização ||| Melhorias para as Instituições ||| melhorias ||| rocessos estruturados e em constante aprimoramento</t>
+          <t>Apoio e suporte da alta gestão da SEPLAN ||| Apoio institucional da alta gestão, favorecendo a implementação das iniciativas estratégicas e o fortalecimento do EPROC no âmbito estadual. ||| Estar vinculado à SEPLAN confere autoridade técnica para disseminar metodologias de gestão por processos em outros órgãos ||| Estrutura de suporte e governança. ||| Governança ||| Patrocínio da alta gestão ||| Posicionamento institucional forte e legítimo ||| Suporte interno</t>
         </is>
       </c>
     </row>
@@ -600,18 +600,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Apoio da alta gestão e governança</t>
+          <t>Capilaridade institucional e rede de NUPROCs</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Apoio e suporte da alta gestão da SEPLAN ||| Apoio institucional da alta gestão, favorecendo a implementação das iniciativas estratégicas e o fortalecimento do EPROC no âmbito estadual. ||| Estar vinculado à SEPLAN confere autoridade técnica para disseminar metodologias de gestão por processos em outros órgãos ||| Estrutura de suporte e governança. ||| Fortalecimento da governança por processos em nível estadual ||| Governança ||| Patrocínio da alta gestão ||| Posicionamento institucional forte e legítimo ||| Ser responsável pela implementação do Modelo de Governança por Processos no Poder executivo estadual. ||| Suporte interno</t>
+          <t>Capilaridade Institucional: A atuação distribuída permite presença em diversos órgãos, ampliando alcance e impacto das melhorias. ||| Modelo descentralizado de atuação nos órgãos do estado ||| Modelo estruturado e escalável (NUPROCs + metodologia) ||| Possibilidade de atuar em apoios a diversos órgãos ||| Presenção em vários orgãos (Capilaridade institucional) - NUPROCs ||| Rede Colaborativa: A estrutura conta com os NUPROCs (Núcleos de Gestão de Processos) em diversos órgãos, formando uma rede que amplia o alcance das ações de melhoria ||| Suporte técnico da equipe do Eproc aos Nuproc’s.</t>
         </is>
       </c>
     </row>
@@ -621,18 +621,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Integração e articulação institucional</t>
+          <t>Disseminação da cultura de gestão por processos</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atuação integrada com base em indicadores, dados e articulação intersetorial, fortalecendo a tomada de decisão ||| Equipe especializada em BPMN com capacidade de disseminação metodológica. Integração estratégica EPROC/SEPLAN/órgãos para alinhamento de prioridades e otimização de fluxos. Padronização de documentos e roteiros com rastreabilidade, qualidade. Experiência em modernização administrativa com entregas de ganhos de eficiência mensuráveis. Articulação interinstitucional para soluções transversais, reduzindo retrabalho. ||| Integração ||| Integração com órgãos parceiros. ||| Integração e cooperação entre os membros da equipe, favorecendo a fluidez dos processos e a resolutividade das demandas. ||| Integração institucional e articulação eficiente entre órgãos governamentais, facilitando a implementação de políticas públicas. ||| Integração institucional entre órgãos e áreas, com atuação em todo o ciclo de planejamento e gestão. ||| O escritório possui atuação junto a diferentes órgãos do governo, o que amplia sua visão sistêmica da administração pública e fortalece sua capacidade de integração, padronização e disseminação de boas práticas ||| conexões/interações ||| relações interpessoais</t>
+          <t>Condução bem definida na implantação da gestão por processos ||| Disseminação da cultura de processos ||| Fortalecimento da governança por processos em nível estadual ||| Liderança em mapeamento de processos ||| Referencia referência em gestão de processos no nível estadual ||| Ser responsável pela implementação do Modelo de Governança por Processos no Poder executivo estadual.</t>
         </is>
       </c>
     </row>
@@ -642,18 +642,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capilaridade institucional e rede de NUPROCs</t>
+          <t>Capacitação e formação continuada</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atuação transversal, com potencial de alcançar diferentes áreas da administração pública e promover alinhamento entre gestão, planejamento e execução ||| Capilaridade Institucional: A atuação distribuída permite presença em diversos órgãos, ampliando alcance e impacto das melhorias. ||| Elaboração do Planejamento Estratégico dos Nuproc’s pelo Eproc ||| Modelo descentralizado de atuação nos órgãos do estado ||| Modelo estruturado e escalável (NUPROCs + metodologia) ||| Possibilidade de atuar em apoios a diversos órgãos ||| Presenção em vários orgãos (Capilaridade institucional) - NUPROCs ||| Rede Colaborativa: A estrutura conta com os NUPROCs (Núcleos de Gestão de Processos) em diversos órgãos, formando uma rede que amplia o alcance das ações de melhoria ||| Suporte técnico da equipe do Eproc aos Nuproc’s.</t>
+          <t>.Capacidade consolidada de produção de materiais técnicos e treinamentos robustos que garantem a padronização e a autonomia na utilização do sistema. ||| Capacitação ||| Capacitação contínua dos especialistas ||| Elevado nível de sensibilização das Diretorias quanto à importância do mapeamento de processos. ||| Preocupação da gestão com a formação inicial e qualificação da equipe, favorecendo alinhamento técnico e padronização dos processos desde a implementação do setor.</t>
         </is>
       </c>
     </row>
@@ -667,56 +667,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Agilidade na resposta a demandas estratégicas, com prazos cumpridos e qualidade técnica. Competência em traduzir necessidades institucionais em processos claros, eficientes e documentados. Capacidade de inovação na aplicação de ferramentas de gestão e tecnologias de suporte a processos. Comprometimento da equipe com resultados institucionais e com a melhoria do serviço público. ||| Disponibilidade e uso estratégico de informações e sistemas para apoio à tomada de decisão baseada em evidências. ||| Ecossistema de Ferramentas: Disponibiliza ferramentas especializadas para gestão e modelagem, como Taiga (gerenciamento), Camunda (modelagem) e painéis de Business Intelligence (BI) para monitoramento ||| Existência de especialistas que dominam notações como BPMN e ferramentas de modelagem ||| Governança de processos com papéis, responsabilidades e fluxos de aprovação definidos. Cultura de melhoria contínua com registro e compartilhamento de lições aprendidas. Infraestrutura tecnológica adequada para modelagem, análise e monitoramento de processos. Alinhamento das atividades do EPROC aos objetivos estratégicos da SEPLAN. ||| Tecnologia ||| Utilização de ferramentas especificas, como o camunda e Taiga, que auxiliam na organização, no acompanhamento das atividades.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Capacitação e formação continuada</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>.Capacidade consolidada de produção de materiais técnicos e treinamentos robustos que garantem a padronização e a autonomia na utilização do sistema. ||| Capacitação ||| Capacitação contínua dos especialistas ||| Elevado nível de sensibilização das Diretorias quanto à importância do mapeamento de processos. ||| Preocupação da gestão com a formação inicial e qualificação da equipe, favorecendo alinhamento técnico e padronização dos processos desde a implementação do setor. ||| Transformação</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Disseminação da cultura de gestão por processos</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Disseminação da cultura de processos ||| Liderança em mapeamento de processos ||| Referencia referência em gestão de processos no nível estadual</t>
+          <t>Ecossistema de Ferramentas: Disponibiliza ferramentas especializadas para gestão e modelagem, como Taiga (gerenciamento), Camunda (modelagem) e painéis de Business Intelligence (BI) para monitoramento ||| Existência de especialistas que dominam notações como BPMN e ferramentas de modelagem ||| Tecnologia ||| Utilização de ferramentas especificas, como o camunda e Taiga, que auxiliam na organização, no acompanhamento das atividades.</t>
         </is>
       </c>
     </row>
@@ -731,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,14 +729,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>16.3</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Alta dependência de bolsistas que pode resultar em  alta rotatividade de pessoas ||| Alta rotatividade de especilistas ||| Alta rotatividade dos servidores terceirizados ||| Alta rotatividade na equipe (coordenação, espcialistas, etc...) ||| Capacidade operacional reduzida em relação ao volume de demandas, impactando a execução e a eficiência dos processos. ||| Carência de servidores em áreas estratégicas devido a aposentadorias. ||| Dependência de estruturas de pessoal e de capacidade operacional para acompanhar Todas as demandas ||| Déficit de pessoal ||| Déficit no quadro de servidores especializados para acompanhamento presencial ou dedicado nos órgãos, limitando a capacidade de suporte consultivo e monitoramento contínuo. ||| Equipe com muitos colaboradores temporários ||| Falta de servidor efetivo para retenção do conhecimento adquirido ||| Limitação de recursos humanos e sobrecarga de demandas ||| Número reduzido de especialistas de apoio, dificultando o atendimento rápido quando necessário ||| O reduzido número de especialistas, aliado à acumulação de atribuições, limita a capacidade de realização de feedbacks estruturados e tempestivos sobre as entregas, impactando o ciclo de melhoria contínua. ||| Os editais para bolsistas possuem vigência de apenas um ano. Uma oportunidade de melhoria seria a ampliação desse prazo para dois anos, utilizando como referência o modelo já adotado pelo EPROJ. Essa mudança garantiria a continuidade e a manutenção por mais tempo dos projetos iniciados nos órgãos. ||| Pouco coro funcional efetivamente da Seplan ||| Poucos efetivos no time ||| Quantidade de servidores efetivos ||| Quantidade reduzida de equipe para atender a demanda. ||| Restrição de recursos humanos e/ou sobrecarga de equipes frente à demanda de atividades. ||| Rotatividade de especialistas. ||| Vínculo do time (frágil e temporário) ||| falta de servidor efetivo ||| poucos servidores e muita rotatividade de terceirizados ||| rotatividade</t>
+          <t>Alta dependência de bolsistas que pode resultar em  alta rotatividade de pessoas ||| Alta rotatividade de especilistas ||| Alta rotatividade dos servidores terceirizados ||| Alta rotatividade na equipe (coordenação, espcialistas, etc...) ||| Capacidade operacional reduzida em relação ao volume de demandas, impactando a execução e a eficiência dos processos. ||| Carência de servidores em áreas estratégicas devido a aposentadorias. ||| Dependência de estruturas de pessoal e de capacidade operacional para acompanhar Todas as demandas ||| Déficit de pessoal ||| Déficit no quadro de servidores especializados para acompanhamento presencial ou dedicado nos órgãos, limitando a capacidade de suporte consultivo e monitoramento contínuo. ||| Equipe com muitos colaboradores temporários ||| Falta de servidor efetivo para retenção do conhecimento adquirido ||| Falta de um copo técnico de servidores efetivos ||| Limitação de recursos humanos e sobrecarga de demandas ||| Número reduzido de especialistas de apoio, dificultando o atendimento rápido quando necessário ||| O reduzido número de especialistas, aliado à acumulação de atribuições, limita a capacidade de realização de feedbacks estruturados e tempestivos sobre as entregas, impactando o ciclo de melhoria contínua. ||| Os editais para bolsistas possuem vigência de apenas um ano. Uma oportunidade de melhoria seria a ampliação desse prazo para dois anos, utilizando como referência o modelo já adotado pelo EPROJ. Essa mudança garantiria a continuidade e a manutenção por mais tempo dos projetos iniciados nos órgãos. ||| Pouco coro funcional efetivamente da Seplan ||| Poucos efetivos no time ||| Quantidade de servidores efetivos ||| Quantidade reduzida de equipe para atender a demanda. ||| Restrição de recursos humanos e/ou sobrecarga de equipes frente à demanda de atividades. ||| Rotatividade de especialistas. ||| Vínculo do time (frágil e temporário) ||| falta de servidor efetivo ||| poucos servidores e muita rotatividade de terceirizados ||| rotatividade</t>
         </is>
       </c>
     </row>
@@ -792,14 +750,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>13.1</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Acompanhamento muito espaçado ||| Ausência de Feedbacks aos especialistas sobre os relatporios e materiais produzidos e encaminhados ||| Ausência de acompanhamento individualizado dos especialistas, dificultando o alinhamento de expectativas e o monitoramento das demandas. ||| Ausência de feedback sobre os relatórios entregues pelos especialistas. ||| Ausência de feedback técnico dos entregáveis, para avaliar a adequação do conteúdo e das sugestões apresentadas. pelos especialistas alocados nos órgãos. ||| Barreiras de Comunicação: Existe uma dificuldade relatada por gestores em comunicar o funcionamento do negócio e a geração de valor de forma clara e simples ||| Comunicação ||| Comunicação e integração entre setores ainda pouco estruturadas, impactando a fluidez dos processos. ||| Dificuldade de manter alinhamento conceitual e motivacional em uma rede capilarizada de especialistas ||| Falta de alinhamento com a alta gestão do órgão ||| Falta de alinhamento entre servidores e terceirizados ||| Fragilidades de comunicação interna ||| Interrupção das reuniões periódicas de alinhamento sobre o material compartilhado e explicação dos entregáveis,  comprometendo a comunicação e a clareza sobre os entregáveis. ||| Oportunidade de ampliar a capacidade de atendimento para acompanhar o crescimento das demandas. Desafio de harmonizar fluxos entre órgãos com diferentes estágios de maturidade em gestão. Espaço para fortalecimento da capacitação contínua em novas ferramentas e metodologias. Oportunidade de tornar a comunicação com áreas demandantes mais ágil e alinhada. ||| Organização das demandas e alinhamento das ações estratégicas. ||| Oscilação na aplicação de diretrizes, gerando dúvidas ||| comunicação e alinhamento entre todos ||| comunicação interna ainda um pouco falha ||| falta de alinhamento entre equipe ||| falta de comunicação</t>
+          <t>Acompanhamento muito espaçado ||| Ausência de Feedbacks aos especialistas sobre os relatporios e materiais produzidos e encaminhados ||| Ausência de acompanhamento individualizado dos especialistas, dificultando o alinhamento de expectativas e o monitoramento das demandas. ||| Ausência de feedback sobre os relatórios entregues pelos especialistas. ||| Ausência de feedback técnico dos entregáveis, para avaliar a adequação do conteúdo e das sugestões apresentadas. pelos especialistas alocados nos órgãos. ||| Barreiras de Comunicação: Existe uma dificuldade relatada por gestores em comunicar o funcionamento do negócio e a geração de valor de forma clara e simples ||| Comunicação ||| Comunicação e integração entre setores ainda pouco estruturadas, impactando a fluidez dos processos. ||| Dificuldade de manter alinhamento conceitual e motivacional em uma rede capilarizada de especialistas ||| Falta de alinhamento com a alta gestão do órgão ||| Falta de alinhamento entre servidores e terceirizados ||| Fragilidades de comunicação interna ||| Interrupção das reuniões periódicas de alinhamento sobre o material compartilhado e explicação dos entregáveis,  comprometendo a comunicação e a clareza sobre os entregáveis. ||| Oportunidade de ampliar a capacidade de atendimento para acompanhar o crescimento das demandas. Desafio de harmonizar fluxos entre órgãos com diferentes estágios de maturidade em gestão. Espaço para fortalecimento da capacitação contínua em novas ferramentas e metodologias. Oportunidade de tornar a comunicação com áreas demandantes mais ágil e alinhada. ||| Organização das demandas e alinhamento das ações estratégicas. ||| Oscilação na aplicação de diretrizes, gerando dúvidas ||| Rruniões maosnfrequentes (quinzenal) sobre o  fluxo de trabalho ||| Sensibilização nos órgãos - deixar de maneira mais clara o papel dos especialistas nos órgãos, antes do início das atividades, pois percebo que ainda há ruído nisso ||| comunicação e alinhamento entre todos ||| comunicação interna ainda um pouco falha ||| falta de alinhamento entre equipe ||| falta de comunicação</t>
         </is>
       </c>
     </row>
@@ -809,18 +767,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Não classificado (revisar manualmente)</t>
+          <t>Ausência de sistema próprio e baixa automação</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baixo nível de padronização e formalização dos processos institucionais. ||| Conciliação do Plano de Trabalho as atividades em órgãos que já tiverem etapas realizadas. ||| Falta de engajamento das empresas do Ecossistema de Inovação ||| Falta de um copo técnico de servidores efetivos ||| Fragilidade ||| Fraqueza é a incapacidade de agir com transparência e coragem, permitindo que a omissão e o medo enfraqueçam sua missão. ||| Fraqueza é a perda de princípios. ||| Fraqueza é quando a desunião e a falta de responsabilidade corroem a confiança e impedem o cumprimento do seu propósito. ||| Incapacidade ||| Legislação frágil e desatualizada ||| Licenciamentos Ambientais ||| Muitas vezes limitações para desempenhar o seu trabalho ||| Necessidade de ampliar a padronização e a integração dos processos entre áreas e órgãos parceiros. ||| Necessidade de aprimoramento na padronização e organização de fluxos internos de trabalho. ||| Risco de Foco em Atividade: O manual alerta para o perigo de focar apenas no mapeamento (fluxogramas) em vez da transformação real das rotinas e resultados ||| Rruniões maosnfrequentes (quinzenal) sobre o  fluxo de trabalho ||| Sensibilização nos órgãos - deixar de maneira mais clara o papel dos especialistas nos órgãos, antes do início das atividades, pois percebo que ainda há ruído nisso ||| poucos departamentos /setores na "Central"</t>
+          <t>Ausência de sistema próprio para gestão integrada dos processos. ||| Ausência de um sistema próprio para a automatização dos processos mapeados. ||| Ausência ou limitação de ferramentas tecnológicas adequadas ||| Baixo nível de automação das atividades operacionais. ||| Conhecimento em Tecnologia/Automação ||| Deficiência/ausência de um sistema interno de gestão de processos ||| Dependência de Viabilidade: Iniciativas de melhoria podem ser paralisadas ou atrasadas se não houver confirmação de viabilidade técnica, financeira ou aceitação da automação pelas partes interessadas ||| Dependência de diferentes sistemas não integrados, comprometendo a celeridade operacional. ||| Dependência de processos manuais e baixa automação em algumas atividades. ||| Dificuldade na integração de dados entre diferentes plataformas de gestão (SIGRH, SGPe e sistemas próprios). ||| Equipe técnica em fase de aprendizado frente a demandas crescentes, impactando prazos e atendimento. Dependência de sistemas que limitam automação e integração de dados. Falta de indicadores padronizados para monitoramento da eficácia dos processos. Documentação descentralizada para apoio aos bolsistas dos órgãos. ||| Excesso de etapas manuais em processos que poderiam ser automatizados ou simplificados. ||| Falta de integração entre sistemas, gerando retrabalho e perda de eficiência. ||| Inexistência de uma ferramenta BPMS implementada ||| Limitações na utilização de ferramentas tecnológicas</t>
         </is>
       </c>
     </row>
@@ -830,18 +788,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ausência de sistema próprio e baixa automação</t>
+          <t>Estrutura interna e governança em consolidação</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ausência de sistema próprio para gestão integrada dos processos. ||| Ausência de um sistema próprio para a automatização dos processos mapeados. ||| Ausência ou limitação de ferramentas tecnológicas adequadas ||| Baixo nível de automação das atividades operacionais. ||| Conhecimento em Tecnologia/Automação ||| Deficiência/ausência de um sistema interno de gestão de processos ||| Dependência de Viabilidade: Iniciativas de melhoria podem ser paralisadas ou atrasadas se não houver confirmação de viabilidade técnica, financeira ou aceitação da automação pelas partes interessadas ||| Dependência de diferentes sistemas não integrados, comprometendo a celeridade operacional. ||| Dependência de processos manuais e baixa automação em algumas atividades. ||| Dificuldade na integração de dados entre diferentes plataformas de gestão (SIGRH, SGPe e sistemas próprios). ||| Equipe técnica em fase de aprendizado frente a demandas crescentes, impactando prazos e atendimento. Dependência de sistemas que limitam automação e integração de dados. Falta de indicadores padronizados para monitoramento da eficácia dos processos. Documentação descentralizada para apoio aos bolsistas dos órgãos. ||| Excesso de etapas manuais em processos que poderiam ser automatizados ou simplificados. ||| Falta de integração entre sistemas, gerando retrabalho e perda de eficiência. ||| Inexistência de uma ferramenta BPMS implementada ||| Limitações na utilização de ferramentas tecnológicas</t>
+          <t>Ausência de coordenação formal ||| Ausência ou inconsistência na priorização das demandas recebidas, podendo gerar impacto na organização das atividades e nos prazos de entrega. (Plano de trabalho). ||| Balanceamento entre necessidades dos órgãos e aderência a metodologia. ||| Conflito de competência ||| Falta de coordenador ||| Falta de estrutura bem definida ||| Legislação frágil e desatualizada ||| Não ter gerência sobre o site do Eproc ||| Por se tratar de uma iniciativa pioneira no Estado, há ausência de modelos e referenciais previamente consolidados, o que demanda o desenvolvimento, validação e aprimoramento contínuo de metodologias e materiais pelo próprio EPROC. ||| Risco de sobrecarga funcional e ambiguidade decisória, em função de responsabilidades elevadas sem estrutura correspondente ||| falta de coordenador ||| falta de referência clara para suporte/decisão ||| gestão centralizada</t>
         </is>
       </c>
     </row>
@@ -851,18 +809,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Estrutura interna e governança em consolidação</t>
+          <t>Sobrecarga e excesso de demandas</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ausência de coordenação formal ||| Ausência ou inconsistência na priorização das demandas recebidas, podendo gerar impacto na organização das atividades e nos prazos de entrega. (Plano de trabalho). ||| Balanceamento entre necessidades dos órgãos e aderência a metodologia. ||| Conflito de competência ||| Falta de coordenador ||| Falta de estrutura bem definida ||| Não ter gerência sobre o site do Eproc ||| Por se tratar de uma iniciativa pioneira no Estado, há ausência de modelos e referenciais previamente consolidados, o que demanda o desenvolvimento, validação e aprimoramento contínuo de metodologias e materiais pelo próprio EPROC. ||| Risco de sobrecarga funcional e ambiguidade decisória, em função de responsabilidades elevadas sem estrutura correspondente ||| falta de coordenador ||| falta de referência clara para suporte/decisão ||| gestão centralizada</t>
+          <t>A equipe atua em múltiplas frentes simultaneamente, o que pode gerar sobrecarga operacional e restringir a dedicação a atividades estratégicas, como avaliação de resultados e aperfeiçoamento metodológico. ||| Acúmulo de atividades técnicas e operacionais no setor. ||| Algumas vezes o volume de demandas de diversas secretarias excede o número de analistas disponíveis ||| Alta demanda de trabalho ||| Alta demanda/Complexidade de processos (demora) ||| Dependência do núcleo central: gargalos e sobrecarga no núcleo. ||| Eproc com muita demanda ||| Muitas vezes limitações para desempenhar o seu trabalho ||| Sobrecarga de Demandas</t>
         </is>
       </c>
     </row>
@@ -914,18 +872,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sobrecarga e excesso de demandas</t>
+          <t>Baixa maturidade em gestão por processos nos órgãos</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A equipe atua em múltiplas frentes simultaneamente, o que pode gerar sobrecarga operacional e restringir a dedicação a atividades estratégicas, como avaliação de resultados e aperfeiçoamento metodológico. ||| Acúmulo de atividades técnicas e operacionais no setor. ||| Algumas vezes o volume de demandas de diversas secretarias excede o número de analistas disponíveis ||| Alta demanda de trabalho ||| Alta demanda/Complexidade de processos (demora) ||| Dependência do núcleo central: gargalos e sobrecarga no núcleo. ||| Eproc com muita demanda ||| Sobrecarga de Demandas</t>
+          <t>Aprimoramento na adaptação às realidades institucionais ||| Baixa adesão de algumas áreas às práticas de gestão por processos. ||| Baixo nível de maturidade em cultura de gestão por processos na maioria dos órgãos atendidos, gerando dificuldades de entendimento e de adesão ás metodologias propostas. ||| Baixo nível de maturidade em gestão de processos nos órgãos ||| Diferenças no nível de conhecimento entre os órgãos exigem esforços adicionais de capacitação e alinhamento ||| Heterogeneidade de capacidade entre órgãos: Diferenças de engajamento, qualificação e priorização dificultam a execução uniforme. ||| Metodologia não está plenamente pronta para órgãos de maior nível de maturidade e/ou que demandem a transformação digital e mensuração de ganhos do AS IS para TO BE</t>
         </is>
       </c>
     </row>
@@ -935,7 +893,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Baixa maturidade em gestão por processos nos órgãos</t>
+          <t>Baixa padronização e desestruturação de fluxos</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -946,7 +904,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aprimoramento na adaptação às realidades institucionais ||| Baixa adesão de algumas áreas às práticas de gestão por processos. ||| Baixo nível de maturidade em cultura de gestão por processos na maioria dos órgãos atendidos, gerando dificuldades de entendimento e de adesão ás metodologias propostas. ||| Baixo nível de maturidade em gestão de processos nos órgãos ||| Diferenças no nível de conhecimento entre os órgãos exigem esforços adicionais de capacitação e alinhamento ||| Heterogeneidade de capacidade entre órgãos: Diferenças de engajamento, qualificação e priorização dificultam a execução uniforme. ||| Metodologia não está plenamente pronta para órgãos de maior nível de maturidade e/ou que demandem a transformação digital e mensuração de ganhos do AS IS para TO BE</t>
+          <t>Baixo nível de padronização e formalização dos processos institucionais. ||| Conciliação do Plano de Trabalho as atividades em órgãos que já tiverem etapas realizadas. ||| Licenciamentos Ambientais ||| Necessidade de ampliar a padronização e a integração dos processos entre áreas e órgãos parceiros. ||| Necessidade de aprimoramento na padronização e organização de fluxos internos de trabalho. ||| Risco de Foco em Atividade: O manual alerta para o perigo de focar apenas no mapeamento (fluxogramas) em vez da transformação real das rotinas e resultados ||| poucos departamentos /setores na "Central"</t>
         </is>
       </c>
     </row>
@@ -1019,7 +977,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Limitação de recursos orçamentários e estruturais</t>
+          <t>Engajamento, responsabilidade e cultura de equipe falhos</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1030,7 +988,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Escassez de recursos orçamentários destinados à capacitação avançada e ao desenvolvimento de ferramentas tecnológicas voltadas especificamente para a otimização da gestão de processos. ||| Infraestrutura Incompleta ||| Limitação de recursos ||| Limitação de recursos (humanos e/ou tecnológicos) para atender todas as demandas. ||| Recursos internos limitados ||| Recursos/investimento</t>
+          <t>Falta de engajamento das empresas do Ecossistema de Inovação ||| Fragilidade ||| Fraqueza é a incapacidade de agir com transparência e coragem, permitindo que a omissão e o medo enfraqueçam sua missão. ||| Fraqueza é a perda de princípios. ||| Fraqueza é quando a desunião e a falta de responsabilidade corroem a confiança e impedem o cumprimento do seu propósito. ||| Incapacidade</t>
         </is>
       </c>
     </row>
@@ -1040,18 +998,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Descontinuidade por mudança de gestão</t>
+          <t>Limitação de recursos orçamentários e estruturais</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Descontinuidade de ações e iniciativas por mudanças de gestão ||| Falta de continuidade nos processos na troca de gestor ||| Troca de comando</t>
+          <t>Escassez de recursos orçamentários destinados à capacitação avançada e ao desenvolvimento de ferramentas tecnológicas voltadas especificamente para a otimização da gestão de processos. ||| Infraestrutura Incompleta ||| Limitação de recursos ||| Limitação de recursos (humanos e/ou tecnológicos) para atender todas as demandas. ||| Recursos internos limitados ||| Recursos/investimento</t>
         </is>
       </c>
     </row>
@@ -1061,18 +1019,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Baixa visibilidade e comunicação externa</t>
+          <t>Descontinuidade por mudança de gestão</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
         <v>2</v>
       </c>
-      <c r="D16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Proposta de valor pouco traduzida para o público externo ( Linguagem técnica ,Baixa comunicação de “benefícios concretos”) ||| Visibilidade</t>
+          <t>Descontinuidade de ações e iniciativas por mudanças de gestão ||| Falta de continuidade nos processos na troca de gestor ||| Troca de comando</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1040,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Resistência à mudança</t>
+          <t>Baixa visibilidade e comunicação externa</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1092,6 +1050,27 @@
         <v>1.3</v>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>Proposta de valor pouco traduzida para o público externo ( Linguagem técnica ,Baixa comunicação de “benefícios concretos”) ||| Visibilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Resistência à mudança</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Dificuldade de alguns setores em abandonar métodos tradicionais ||| Forte resistência à mudança por parte dos servidores</t>
         </is>
@@ -1108,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,14 +1127,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>15.9</v>
+        <v>17.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adoção de ferramentas de Inteligência Artificial para otimizar a análise de projetos e editais culturais. ||| Adoção de novas tecnologias (IA, Big Data, BPMS) ||| Adoção de novas tecnologias. ||| Aproveitamento do grande volume de processos mapeados em BPMN para a automação desses fluxos por meio de um sistema próprio. ||| Avanço das  tecnologias digitais e das soluções de  automação de processos, possibilitando maior eficiência  e modernização da gestão pública ||| Avanço das tecnologias digitais e de análise de dados aplicadas ao planejamento e à gestão pública ||| Avanço de tecnologias digitais e automação de processos ||| Avanço de tecnologias digitais e ferramentas de análise de dados que potencializam a modernização da gestão pública. ||| Avanço de tecnologias e ferramentas digitais voltadas à gestão e automação de processos. ||| Avanço tecnológico e digitalização dos serviços públicos, permitindo automação de processos, aumento de eficiência operacional e melhoria no atendimento ao cidadão. ||| Cenários de limitação de recursos públicos podem impactar investimentos em capacitação, tecnologia e expansão das iniciativas de gestão por processos. ||| Crescente agenda de transformação digital no setor público ||| Expansão do Governo Digital priorizando simplificação e eficiência de processos. Adoção de ferramentas colaborativas e em nuvem para facilitar integração e trabalho remoto. Estímulo normativo à transparência, aumentando demanda por processos documentados e auditáveis. Modernização legislativa abrindo espaço para revisão e otimização de fluxos administrativos. ||| Fortalecimento da Gestão de Processos pela necessidade de transformação digital  do governo de SC ||| O avanço da transformação digital no Estado permite ao EPROC melhorar e automatizar processos. ||| O avanço de tecnologias como automação de processos (RPA), inteligência artificial e análise de dados cria uma oportunidade clara para o escritório de processos atuar como protagonista na transformação digital do governo. A crescente adoção de plataformas digitais no setor público, além da expansão do conceito de governo digital no Brasil, permite padronizar fluxos, reduzir retrabalho e aumentar a transparência. Em SC, que já tem um ecossistema tecnológico forte, há espaço para integrar soluções inovadoras aos processos internos, posicionando o escritório como articulador entre tecnologia e gestão. ||| Transformação Digital ||| Transformação Digital: A adoção de tecnologias avançadas, como inteligência artificial e agentes inteligentes, permite inovar e otimizar processos de forma disruptiva ||| Transformação Digital: O foco governamental em automação, IA e serviços digitais cria um ambiente propício para a modernização acelerada dos fluxos de trabalho ||| Uso de tecnologias (automação, BPM, dados) ||| Uso de tecnologias de informação e gestão do conhecimento ||| ferramentas digitais ||| tecnologia e automação ||| transformação digital</t>
+          <t>Adoção de ferramentas de Inteligência Artificial para otimizar a análise de projetos e editais culturais. ||| Adoção de novas tecnologias (IA, Big Data, BPMS) ||| Adoção de novas tecnologias. ||| Aproveitamento do grande volume de processos mapeados em BPMN para a automação desses fluxos por meio de um sistema próprio. ||| Avanço das  tecnologias digitais e das soluções de  automação de processos, possibilitando maior eficiência  e modernização da gestão pública ||| Avanço das ferramentas tecnológicas ||| Avanço das tecnologias digitais e de análise de dados aplicadas ao planejamento e à gestão pública ||| Avanço de ferramentas e metodologias de planejamento e gestão pública, que fortalecem a atuação estratégica da SEPLAN junto aos órgãos ||| Avanço de tecnologias digitais e automação de processos ||| Avanço de tecnologias digitais e ferramentas de análise de dados que potencializam a modernização da gestão pública. ||| Avanço de tecnologias e ferramentas digitais voltadas à gestão e automação de processos. ||| Avanço tecnológico e digitalização dos serviços públicos, permitindo automação de processos, aumento de eficiência operacional e melhoria no atendimento ao cidadão. ||| Cenários de limitação de recursos públicos podem impactar investimentos em capacitação, tecnologia e expansão das iniciativas de gestão por processos. ||| Crescente agenda de transformação digital no setor público ||| Expansão do Governo Digital priorizando simplificação e eficiência de processos. Adoção de ferramentas colaborativas e em nuvem para facilitar integração e trabalho remoto. Estímulo normativo à transparência, aumentando demanda por processos documentados e auditáveis. Modernização legislativa abrindo espaço para revisão e otimização de fluxos administrativos. ||| Fortalecimento da Gestão de Processos pela necessidade de transformação digital  do governo de SC ||| O avanço da transformação digital no Estado permite ao EPROC melhorar e automatizar processos. ||| O avanço de tecnologias como automação de processos (RPA), inteligência artificial e análise de dados cria uma oportunidade clara para o escritório de processos atuar como protagonista na transformação digital do governo. A crescente adoção de plataformas digitais no setor público, além da expansão do conceito de governo digital no Brasil, permite padronizar fluxos, reduzir retrabalho e aumentar a transparência. Em SC, que já tem um ecossistema tecnológico forte, há espaço para integrar soluções inovadoras aos processos internos, posicionando o escritório como articulador entre tecnologia e gestão. ||| Transformação Digital ||| Transformação Digital: A adoção de tecnologias avançadas, como inteligência artificial e agentes inteligentes, permite inovar e otimizar processos de forma disruptiva ||| Transformação Digital: O foco governamental em automação, IA e serviços digitais cria um ambiente propício para a modernização acelerada dos fluxos de trabalho ||| Uso de tecnologias (automação, BPM, dados) ||| Uso de tecnologias de informação e gestão do conhecimento ||| ferramentas digitais ||| tecnologia e automação ||| transformação digital</t>
         </is>
       </c>
     </row>
@@ -1169,14 +1148,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A ampliação de parcerias institucionais e programas de fomento fortalece a atuação do EPROC na disseminação da cultura de gestão por processos. ||| Ampliar parcerias com Universidades, órgãos governamentais para aumentar o acesso a recursos e infraestrutura esportiva ||| Ampliação de parcerias institucionais ||| Ampliação de parcerias institucionais com órgãos, universidades e entidades para desenvolvimento de projetos estratégicos. ||| Colaboração com a ENA (Escola de Governo) para capacitação de servidores em gestão de processos ||| Conexão ||| Integração interinstitucional ||| Interação ||| Maior contato nas instituições ||| Networking ||| Parcerias  as com órgãos e entidades externas ||| Parcerias com outros órgãos ainda não explorados ||| Parcerias com outros órgãos e benchmarking com boas práticas ||| Parcerias com órgãos de controle para troca de boas práticas em gestão de processos. ||| Participar do edital da Fapesc do prêmio de inovação Eric Stemmer de 2026 (prazo: 30jun). Possibilitar maior visibilidade interinstitucional do Eproc e validação por atores externos ||| Possibilidade de cooperação com outros órgãos públicos, instituições de referência e redes de gestão, permitindo troca de experiências, acesso a boas práticas e fortalecimento metodológico. ||| Possibilidade de institucionalizar redes de multiplicadores ||| networking ||| parcerias ||| parcerias estratégicas ||| parcerias institucionais ||| Órgãos de controle que exigem mapeamentos</t>
+          <t>Ampliar parcerias com Universidades, órgãos governamentais para aumentar o acesso a recursos e infraestrutura esportiva ||| Ampliação de parcerias institucionais ||| Ampliação de parcerias institucionais com órgãos, universidades e entidades para desenvolvimento de projetos estratégicos. ||| Colaboração com a ENA (Escola de Governo) para capacitação de servidores em gestão de processos ||| Conexão ||| Integração interinstitucional ||| Interação ||| Maior contato nas instituições ||| Networking ||| Parcerias  as com órgãos e entidades externas ||| Parcerias com outros órgãos ainda não explorados ||| Parcerias com outros órgãos e benchmarking com boas práticas ||| Parcerias com órgãos de controle para troca de boas práticas em gestão de processos. ||| Participar do edital da Fapesc do prêmio de inovação Eric Stemmer de 2026 (prazo: 30jun). Possibilitar maior visibilidade interinstitucional do Eproc e validação por atores externos ||| Possibilidade de cooperação com outros órgãos públicos, instituições de referência e redes de gestão, permitindo troca de experiências, acesso a boas práticas e fortalecimento metodológico. ||| Possibilidade de institucionalizar redes de multiplicadores ||| networking ||| parcerias ||| parcerias estratégicas ||| parcerias institucionais ||| Órgãos de controle que exigem mapeamentos</t>
         </is>
       </c>
     </row>
@@ -1186,18 +1165,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crescente demanda por eficiência e transparência</t>
+          <t>Fortalecimento da cultura e governança corporativa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>9.300000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A crescente demanda por transparencia e eficiencia ||| A sociedade está cada vez mais exigente em relação à qualidade, agilidade e transparência dos serviços públicos. Esse cenário favorece o fortalecimento de estruturas que promovam melhoria contínua e foco no cidadão. O escritório de processos pode aproveitar essa pressão externa para impulsionar projetos de simplificação de serviços, redesenho de jornadas do usuário e desburocratização, alinhando-se às expectativas da população e aumentando a percepção de valor do governo. ||| Alta demanda pelos serviços oferecidos ||| Crescente adesão dos órgãos estaduais à solicitação de mapeamento de processos via Eproc, ampliando a atuação da SEPLAN ||| Crescente demanda por eficiência e transparência na gestão pública ||| Crescente demanda por eficiência no setor público ||| Crescente demanda por modernização da gestão pública ||| Crescente demanda por transparência e eficiência na administração pública, fortalecendo iniciativas de planejamento e monitoramento. ||| Demanda por Eficiência (serviços públicos mais ágeis e transparentes legitima a atuação do EPROC) ||| Desejo dos órgãos em terem os processos mapeados ||| Muitos órgãos precisando de apoio nas áreas de atuação do EPROC ||| Pressão por transparência e melhoria dos serviços públicos ||| necessidade de agilidade no setor publico ||| rescente valorização da eficiência e transparência na administração pública.</t>
+          <t>A ampliação de parcerias institucionais e programas de fomento fortalece a atuação do EPROC na disseminação da cultura de gestão por processos. ||| Ambiente externo orientado ao fortalecimento da governança, favorecendo iniciativas de padronização e otimização de processos. ||| Ampliação da cultura de planejamento estratégico nos órgãos ||| Crescente valorização da governança e da gestão por processos no setor público, ampliando a importância estratégica das atividades desenvolvidas pelo EPROC. ||| Crescimento da importancia da gestão de processos ||| Cultura institucional em alguns setores pode dificultar a adoção de novas metodologias, comprometendo a efetividade das iniciativas do EPROC. ||| Fortalecimento da cultura de gestão por processos ||| Fortalecimento da gestão por processos no setor público ||| Fortalecimento das diretrizes de governança no setor público, criando um ambiente propício para modernização e eficiência administrativa. ||| Incentivo à gestão por processos e governança ||| Maior valorização do planejamento ||| Possibilidade de consolidação como referência nacional em gestão por processos no setor público ||| Possibilidade de fortalecimento da gestão por meio da implementação de rotinas sistemáticas de acompanhamento e alinhamento individual com os especialistas. ||| Reestruturação baseada nos processos ||| Tendência de valorização da gestão por processos no setor público, fortalecendo o papel estratégico do EPROC. Avanço da LGPD e normas de governança criando demanda por mapeamento e controle de fluxos de informação. Expansão de comunidades de prática e fóruns de gestão pública para aprendizado colaborativo e benchmarking. Oportunidade de posicionar a SEPLAN como referência estadual em eficiência administrativa e inovação institucional.</t>
         </is>
       </c>
     </row>
@@ -1207,18 +1186,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Não classificado (revisar manualmente)</t>
+          <t>Ampliação de capacitações e disseminação de conhecimento</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ambiente externo orientado ao fortalecimento da governança, favorecendo iniciativas de padronização e otimização de processos. ||| Avanço das ferramentas tecnológicas ||| Avanço de ferramentas e metodologias de planejamento e gestão pública, que fortalecem a atuação estratégica da SEPLAN junto aos órgãos ||| Cultura institucional em alguns setores pode dificultar a adoção de novas metodologias, comprometendo a efetividade das iniciativas do EPROC. ||| Entendimento ||| Fortalecimento das diretrizes de governança no setor público, criando um ambiente propício para modernização e eficiência administrativa. ||| Identificar e suprir lacunas em regiões carentes de programas esportivos ||| Integração com outros órgãos e iniciativas estratégicas do Estado. ||| Integração entre órgãos, para que o órgão se motive a participar as atividades ||| Oportunidade abre caminhos e cria possibilidades para avanço, desde que seja identificado e bem aproveitado. ||| Oportunidade é o momento favorável que permite transformar desafios em crescimento e progresso. ||| Possibilidade de padronização e integração dos processos institucionais a partir das demandas centralizadas no eproc ||| Retomada e sistematização das reuniões de alinhamento para melhoria da comunicação e clareza dos entregáveis.</t>
+          <t>A promoção da linguagem simples no EPROC pode melhorar a qualidade das entregas, tornando as Instruções de Trabalho (IT) e outros artefatos públicos do escritório mais claros, aumentando a transparência e a compreensão do cidadão sobre os serviços públicos. ||| Ampliação de capacitações e espaços de troca técnica, favorecendo o desenvolvimento contínuo da equipe. ||| Ampliação de programas de treinamento pode elevar a maturidade organizacional e reduzir dependência direta do EPROC ||| Disseminação de Conhecimento: Fortalecimento da cultura em Gestão de Processos através de treinamentos conjuntos entre EPROC e órgãos. ||| Entendimento ||| Eventos de capacitação ||| Oportunidade abre caminhos e cria possibilidades para avanço, desde que seja identificado e bem aproveitado. ||| Oportunidade é o momento favorável que permite transformar desafios em crescimento e progresso. ||| Possibilidade de ampliação das ações de capacitação e sensibilização  dos órgãos atendidos, fortalecendo a cultura de gestão por processos. ||| Possibilidade de realizar eventos aberto para compartilhamento de boas práticas em gestão de processo ||| Proporcionar a capacitação a todos os especialistas (e não limitar devido a questão de espaços) ||| Retomada e sistematização das reuniões de alinhamento para melhoria da comunicação e clareza dos entregáveis. ||| capacitação ||| eventos</t>
         </is>
       </c>
     </row>
@@ -1228,18 +1207,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apoio institucional e alinhamento ao plano de governo</t>
+          <t>Crescente demanda por eficiência e transparência</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Apoio instituicional ||| Buscar apoio institucional de entidades (que são autoridade em processos) e instituir e/ ou sediar evento nacional no estado sobre gestão de processos ||| Diretrizes governamentais voltadas à modernização da gestão pública. ||| Fortalecimento institucional por meio de apoio explícito do nível estratégico ||| Necessidade de patrocínio e direcionamento da alta gestão (Governador) - Teria redução de resistências institucionais com apoio do Governador ||| Participação em mais atividades de plano de governo ||| Plano de Governo ||| Plano de governo ||| Politico ||| Programas Estratégicos: Iniciativas como o Avança SC (Estratégia 2035) fornecem um norte claro para que os processos finalísticos gerem valor direto à sociedade ||| Programas de governo ||| plano de governo</t>
+          <t>A crescente demanda por transparencia e eficiencia ||| A sociedade está cada vez mais exigente em relação à qualidade, agilidade e transparência dos serviços públicos. Esse cenário favorece o fortalecimento de estruturas que promovam melhoria contínua e foco no cidadão. O escritório de processos pode aproveitar essa pressão externa para impulsionar projetos de simplificação de serviços, redesenho de jornadas do usuário e desburocratização, alinhando-se às expectativas da população e aumentando a percepção de valor do governo. ||| Alta demanda pelos serviços oferecidos ||| Crescente adesão dos órgãos estaduais à solicitação de mapeamento de processos via Eproc, ampliando a atuação da SEPLAN ||| Crescente demanda por eficiência e transparência na gestão pública ||| Crescente demanda por eficiência no setor público ||| Crescente demanda por modernização da gestão pública ||| Crescente demanda por transparência e eficiência na administração pública, fortalecendo iniciativas de planejamento e monitoramento. ||| Demanda por Eficiência (serviços públicos mais ágeis e transparentes legitima a atuação do EPROC) ||| Desejo dos órgãos em terem os processos mapeados ||| Muitos órgãos precisando de apoio nas áreas de atuação do EPROC ||| Pressão por transparência e melhoria dos serviços públicos ||| necessidade de agilidade no setor publico ||| rescente valorização da eficiência e transparência na administração pública.</t>
         </is>
       </c>
     </row>
@@ -1249,18 +1228,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fortalecimento da cultura de gestão por processos</t>
+          <t>Integração de sistemas e processos unificados</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ampliação da cultura de planejamento estratégico nos órgãos ||| Crescente valorização da governança e da gestão por processos no setor público, ampliando a importância estratégica das atividades desenvolvidas pelo EPROC. ||| Crescimento da importancia da gestão de processos ||| Fortalecimento da cultura de gestão por processos ||| Fortalecimento da gestão por processos no setor público ||| Incentivo à gestão por processos e governança ||| Maior valorização do planejamento ||| Possibilidade de consolidação como referência nacional em gestão por processos no setor público ||| Possibilidade de fortalecimento da gestão por meio da implementação de rotinas sistemáticas de acompanhamento e alinhamento individual com os especialistas. ||| Reestruturação baseada nos processos ||| Tendência de valorização da gestão por processos no setor público, fortalecendo o papel estratégico do EPROC. Avanço da LGPD e normas de governança criando demanda por mapeamento e controle de fluxos de informação. Expansão de comunidades de prática e fóruns de gestão pública para aprendizado colaborativo e benchmarking. Oportunidade de posicionar a SEPLAN como referência estadual em eficiência administrativa e inovação institucional.</t>
+          <t>A unificação da Inteligência de dados (SAPE, EPAGRI, CIDASC) para a reposta ágil aos desafios do século XXI ||| Aquisição de um sistema de gestão de processos ||| Carta de Serviços ||| Com a criação do inventário de processos do órgão, agora temos dados concretos para estimar o tempo médio de mapeamento. Podemos utilizar essas informações para justificar a extensão do vínculo dos bolsistas por um prazo mais adequado. Com esse tempo extra, teremos capacidade para alcançar, se não 100%, pelo menos 80% dos processos mapeados — que é a principal entrega desejada pela instituição —, mantendo um custo significativamente menor se comparado à contratação de uma consultoria. ||| Crescimento da cultura de dados e integração entre sistemas, possibilitando tomadas de decisão mais assertivas, transparência e otimização de recursos. ||| Desenvolver sistema corporativo de uso dos órgãos para acompanhamento de indicadores voltados para melhorias em processos ||| Desenvolvimento de uma plataforma integrada que reúna informações, sistemas, indicadores (BI) ||| Integração com dados e analytics ||| Integração com outros órgãos e iniciativas estratégicas do Estado. ||| Integração de Sistemas: A possibilidade de integrar processos com o SGP-e e o portal SC.GOV.BR pode aumentar significativamente a transparência e agilidade dos serviços ao cidadão ||| Integração entre órgãos, para que o órgão se motive a participar as atividades ||| Possibilidade de padronização e integração dos processos institucionais a partir das demandas centralizadas no eproc ||| Uma intranet como instrumento de cultura e padronização para secretaria.</t>
         </is>
       </c>
     </row>
@@ -1270,18 +1249,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ampliação de capacitações e disseminação de conhecimento</t>
+          <t>Apoio institucional e alinhamento ao plano de governo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A promoção da linguagem simples no EPROC pode melhorar a qualidade das entregas, tornando as Instruções de Trabalho (IT) e outros artefatos públicos do escritório mais claros, aumentando a transparência e a compreensão do cidadão sobre os serviços públicos. ||| Ampliação de capacitações e espaços de troca técnica, favorecendo o desenvolvimento contínuo da equipe. ||| Ampliação de programas de treinamento pode elevar a maturidade organizacional e reduzir dependência direta do EPROC ||| Disseminação de Conhecimento: Fortalecimento da cultura em Gestão de Processos através de treinamentos conjuntos entre EPROC e órgãos. ||| Eventos de capacitação ||| Possibilidade de ampliação das ações de capacitação e sensibilização  dos órgãos atendidos, fortalecendo a cultura de gestão por processos. ||| Possibilidade de realizar eventos aberto para compartilhamento de boas práticas em gestão de processo ||| Proporcionar a capacitação a todos os especialistas (e não limitar devido a questão de espaços) ||| capacitação ||| eventos</t>
+          <t>Apoio instituicional ||| Buscar apoio institucional de entidades (que são autoridade em processos) e instituir e/ ou sediar evento nacional no estado sobre gestão de processos ||| Diretrizes governamentais voltadas à modernização da gestão pública. ||| Fortalecimento institucional por meio de apoio explícito do nível estratégico ||| Necessidade de patrocínio e direcionamento da alta gestão (Governador) - Teria redução de resistências institucionais com apoio do Governador ||| Participação em mais atividades de plano de governo ||| Plano de Governo ||| Plano de governo ||| Politico ||| Programas Estratégicos: Iniciativas como o Avança SC (Estratégia 2035) fornecem um norte claro para que os processos finalísticos gerem valor direto à sociedade ||| Programas de governo ||| plano de governo</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1281,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A expansão para novos esportes e modalidades ||| Ampliar escopo de atuação junto aos órgãos públicos do poder executivo ||| Capilaridade ||| Com a criação do inventário de processos do órgão, agora temos dados concretos para estimar o tempo médio de mapeamento. Podemos utilizar essas informações para justificar a extensão do vínculo dos bolsistas por um prazo mais adequado. Com esse tempo extra, teremos capacidade para alcançar, se não 100%, pelo menos 80% dos processos mapeados — que é a principal entrega desejada pela instituição —, mantendo um custo significativamente menor se comparado à contratação de uma consultoria. ||| Desenvolver e disponibilizar ferramentas tecnológicas para que os Nuproc’s possam colaborar através da informatização de fluxos de atividades para melhoria de processos ||| Expansão ||| Fortalecer os NUPROCs já institucionalizados nos órgãos, para ampliar a capilaridade das ações do EPROC. ||| Suporte Estratégico: Apoio técnico e consultivo aos órgãos na elaboração de seus planejamentos estratégicos, ampliando a relevância do setor. ||| Valorização do EPROC como consultoria interna estratégica de governo ||| alta capilaridade nos órgãos do poder executivo por meio da presença de bolsistas em núcleos de gestão de processos</t>
+          <t>A expansão para novos esportes e modalidades ||| Ampliar escopo de atuação junto aos órgãos públicos do poder executivo ||| Capilaridade ||| Desenvolver e disponibilizar ferramentas tecnológicas para que os Nuproc’s possam colaborar através da informatização de fluxos de atividades para melhoria de processos ||| Expansão ||| Fortalecer os NUPROCs já institucionalizados nos órgãos, para ampliar a capilaridade das ações do EPROC. ||| Identificar e suprir lacunas em regiões carentes de programas esportivos ||| Suporte Estratégico: Apoio técnico e consultivo aos órgãos na elaboração de seus planejamentos estratégicos, ampliando a relevância do setor. ||| Valorização do EPROC como consultoria interna estratégica de governo ||| alta capilaridade nos órgãos do poder executivo por meio da presença de bolsistas em núcleos de gestão de processos</t>
         </is>
       </c>
     </row>
@@ -1312,18 +1291,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Integração de sistemas e uso estratégico de dados</t>
+          <t>Investimentos em infraestrutura e recursos</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A unificação da Inteligência de dados (SAPE, EPAGRI, CIDASC) para a reposta ágil aos desafios do século XXI ||| Aquisição de um sistema de gestão de processos ||| Carta de Serviços ||| Crescimento da cultura de dados e integração entre sistemas, possibilitando tomadas de decisão mais assertivas, transparência e otimização de recursos. ||| Desenvolver sistema corporativo de uso dos órgãos para acompanhamento de indicadores voltados para melhorias em processos ||| Desenvolvimento de uma plataforma integrada que reúna informações, sistemas, indicadores (BI) ||| Integração com dados e analytics ||| Integração de Sistemas: A possibilidade de integrar processos com o SGP-e e o portal SC.GOV.BR pode aumentar significativamente a transparência e agilidade dos serviços ao cidadão ||| Uma intranet como instrumento de cultura e padronização para secretaria.</t>
+          <t>Crescimento do turismo em Santa Catarina como vetor para aumentar a visitação e a visibilidade das casas de cultura. ||| Desenvolvimento do pilaer Arte (e cultura) ||| Economico ||| Ecossistemas de inovação ||| Estimular empresas catarinenses a utilizarem a renúncia fiscal. ||| Investimentos em infraestrutura. ||| Social ||| projetos inovadores</t>
         </is>
       </c>
     </row>
@@ -1333,18 +1312,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Investimentos em infraestrutura e recursos</t>
+          <t>Marcos legais e normativos favoráveis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Crescimento do turismo em Santa Catarina como vetor para aumentar a visitação e a visibilidade das casas de cultura. ||| Desenvolvimento do pilaer Arte (e cultura) ||| Economico ||| Ecossistemas de inovação ||| Estimular empresas catarinenses a utilizarem a renúncia fiscal. ||| Investimentos em infraestrutura. ||| Social ||| projetos inovadores</t>
+          <t>A consolidação de marcos legais como a Lei Geral de Proteção de Dados (LGPD) e a Lei de Acesso à Informação pressiona o setor público a estruturar melhor seus processos, especialmente em relação à rastreabilidade, padronização e segurança da informação. Isso abre uma oportunidade direta para o escritório de processos liderar iniciativas de conformidade (compliance), revisão de fluxos e governança, fortalecendo sua relevância institucional e estratégica dentro do governo estadual. ||| Avanços de normativas que incentivam a governança e gestão por processos ||| Incentivos legais e políticas públicas voltadas à inovação e modernização administrativa, favorecendo parcerias, captação de recursos e implementação de novas soluções. ||| Normas de qualidade exigidas por órgãos externos ||| políticas públicas que promovem a gestão por processos</t>
         </is>
       </c>
     </row>
@@ -1354,18 +1333,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marcos legais e normativos favoráveis</t>
+          <t>Comunicação e divulgação institucional</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A consolidação de marcos legais como a Lei Geral de Proteção de Dados (LGPD) e a Lei de Acesso à Informação pressiona o setor público a estruturar melhor seus processos, especialmente em relação à rastreabilidade, padronização e segurança da informação. Isso abre uma oportunidade direta para o escritório de processos liderar iniciativas de conformidade (compliance), revisão de fluxos e governança, fortalecendo sua relevância institucional e estratégica dentro do governo estadual. ||| Avanços de normativas que incentivam a governança e gestão por processos ||| Incentivos legais e políticas públicas voltadas à inovação e modernização administrativa, favorecendo parcerias, captação de recursos e implementação de novas soluções. ||| Normas de qualidade exigidas por órgãos externos ||| políticas públicas que promovem a gestão por processos</t>
+          <t>Ampliação da comunicação institucional para ensinar a sociedade sobre o que é gestão de processos, sua importância e seus benefícios. ||| Fortalecimento da Publicidade do parque ||| Maior divulgação  do trabalho, atividades da Seplan ||| Programa de engajamento com a Comunidade</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1354,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Comunicação e divulgação institucional</t>
+          <t>Concurso público e fortalecimento do quadro funcional</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1386,7 +1365,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ampliação da comunicação institucional para ensinar a sociedade sobre o que é gestão de processos, sua importância e seus benefícios. ||| Fortalecimento da Publicidade do parque ||| Maior divulgação  do trabalho, atividades da Seplan ||| Programa de engajamento com a Comunidade</t>
+          <t>Ampliação do quadro de pessoal. ||| Oportunidade de fazer um  concurso público para a pasta com o intuito de fortalecer o corpo funcional ||| Possibilidade de concurso público ||| Valorização humana: oportunidade de abertura de concurso público de capital humano efetivo para estruturar a máquina e manter o legado agropecuário.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1375,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Concurso público e fortalecimento do quadro funcional</t>
+          <t>Consolidação como referência nacional</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1406,27 +1385,6 @@
         <v>2.6</v>
       </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>Ampliação do quadro de pessoal. ||| Oportunidade de fazer um  concurso público para a pasta com o intuito de fortalecer o corpo funcional ||| Possibilidade de concurso público ||| Valorização humana: oportunidade de abertura de concurso público de capital humano efetivo para estruturar a máquina e manter o legado agropecuário.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Consolidação como referência nacional</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E15" t="inlineStr">
         <is>
           <t>Consolidar o EPROC como centro de referência técnica na implementação da Política Nacional de Linguagem Simples, integrando a clareza comunicacional ao redesenho de processos para elevar a eficiência operacional e a satisfação do cidadão. ||| Expansão como referência nacional ||| Oportunidade quando reconhecida e aproveitada, pode impulsionar crescimento e resultados positivos. ||| visibilidade por resultados</t>
         </is>
@@ -1443,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,14 +1441,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A troca de governo. ||| Alterações no direcionamento estratégico ou na gestão podem impactar a continuidade e priorização das iniciativas de gestão por processos. ||| Constante mudança no cenário político ||| Descontinuidade administrativa ou mudanças de governo/prioridades, com risco de interrupção de projetos e perda de alinhamento estratégico ||| Descontinuidade das atividades realizadas pelo Eproc e Nuprocs ||| Extinção da Secretaria ||| Falta de apoio por troca de governo ||| Falta de blindagem do EPROC para enfrentar mudanças de gestão ||| Instabilidade política que pode afetar a continuidade de projetos ||| Mudança de Governo ||| Mudança de gestão governamental ||| Mudança na Gestão do escritório ||| Mudança política ||| Mudanças das diretrizes políticas que dificultam a continuidade de algumas ações ||| Mudanças de gestão e prioridades institucionais. ||| Mudanças de gestão governamental que podem alterar as prioridades estratégicas ou reduzir o orçamento do escritório ||| Mudanças de governo ou de prioridades institucionais ||| Mudanças de prioridades governamentais e institucionais ||| Mudanças frequentes de gestão ||| Mudanças frequentes de gestão, prioridades governamentais e descontinuidade administrativa podem comprometer a continuidade de iniciativas de melhoria de processos. A falta de alinhamento estratégico entre secretarias e lideranças também pode gerar baixa adesão às metodologias propostas pelo escritório, dificultando a institucionalização da cultura de gestão por processos no governo. ||| Mudanças frequentes em legislações e normas, exigindo adaptações rápidas dos processos. ||| Mudanças frequentes nas prioridades do governo podem dificultar a continuidade das iniciativas de gestão por processos. ||| Mudanças frequentes no cenário político-administrativo, afetando prioridades e diretrizes institucionais. ||| Mudanças institucionais e políticas ||| Mudanças nas prioridades governamentais que possam impactar a continuidade das iniciativas estratégicas do EPROC. ||| Mudanças no cenário político ||| Mudanças políticas ||| Mudanças políticas e de gestão ||| Mudanças políticas e institucionais ||| Muita mudança no  comando  da pasta em pouco  tempo, pode trazer instabilidade na execução do  trabalho ||| Processo de reestruturação do escritório no início das atividades, ocorrendo paralelamente à alocação dos bolsistas nos órgãos, o que impactou no alinhamento inicial das ações. ||| Troca de Líderes ||| Vulnerabilidade do setor a mudanças de diretrizes políticas, elevando o risco de extinção ou redução de relevância em novas administrações. ||| mudança de governo ||| mudanças políticas ||| rotatividade em funções estratégicas, associada a mudanças de gestão (terceirizados e comissionados) impactando a continuidade das ações e projetos institucionais.</t>
+          <t>A troca de governo. ||| Alterações no direcionamento estratégico ou na gestão podem impactar a continuidade e priorização das iniciativas de gestão por processos. ||| Constante mudança no cenário político ||| Descontinuidade administrativa ou mudanças de governo/prioridades, com risco de interrupção de projetos e perda de alinhamento estratégico ||| Descontinuidade das atividades realizadas pelo Eproc e Nuprocs ||| Extinção da Secretaria ||| Falta de apoio por troca de governo ||| Falta de blindagem do EPROC para enfrentar mudanças de gestão ||| Instabilidade política que pode afetar a continuidade de projetos ||| Mudança de Governo ||| Mudança de gestão governamental ||| Mudança na Gestão do escritório ||| Mudança política ||| Mudanças das diretrizes políticas que dificultam a continuidade de algumas ações ||| Mudanças de diretrizes governamentais ou prioridades institucionais que impactam a continuidade das ações de mapeamento de processos ||| Mudanças de gestão e prioridades institucionais. ||| Mudanças de gestão governamental que podem alterar as prioridades estratégicas ou reduzir o orçamento do escritório ||| Mudanças de governo ou de prioridades institucionais ||| Mudanças de prioridades governamentais e institucionais ||| Mudanças frequentes de gestão ||| Mudanças frequentes de gestão, prioridades governamentais e descontinuidade administrativa podem comprometer a continuidade de iniciativas de melhoria de processos. A falta de alinhamento estratégico entre secretarias e lideranças também pode gerar baixa adesão às metodologias propostas pelo escritório, dificultando a institucionalização da cultura de gestão por processos no governo. ||| Mudanças frequentes em legislações e normas, exigindo adaptações rápidas dos processos. ||| Mudanças frequentes nas prioridades do governo podem dificultar a continuidade das iniciativas de gestão por processos. ||| Mudanças frequentes no cenário político-administrativo, afetando prioridades e diretrizes institucionais. ||| Mudanças institucionais e políticas ||| Mudanças na gestão estadual que podem alterar prioridades e descontinuar iniciativas ||| Mudanças nas prioridades governamentais que possam impactar a continuidade das iniciativas estratégicas do EPROC. ||| Mudanças no cenário político ||| Mudanças políticas ||| Mudanças políticas e de gestão ||| Mudanças políticas e institucionais ||| Muita mudança no  comando  da pasta em pouco  tempo, pode trazer instabilidade na execução do  trabalho ||| Processo de reestruturação do escritório no início das atividades, ocorrendo paralelamente à alocação dos bolsistas nos órgãos, o que impactou no alinhamento inicial das ações. ||| Troca de Líderes ||| Vulnerabilidade do setor a mudanças de diretrizes políticas, elevando o risco de extinção ou redução de relevância em novas administrações. ||| mudança de governo ||| mudanças políticas ||| rotatividade em funções estratégicas, associada a mudanças de gestão (terceirizados e comissionados) impactando a continuidade das ações e projetos institucionais.</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1462,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A falta de recursos pode limitar ações de capacitação, tecnologia e melhoria de processos. ||| A insuficiência de investimentos em soluções como inteligência artificial e automação limita a modernização dos processos e reduz o potencial de ganho de eficiência institucional. ||| Conflito por recursos e atenção com outras áreas e programas do governo, que podem diluir o foco nas iniciativas do EPROC ||| Falta de investimento financeiro do governo do estado ||| Falta de recursos para dar continuidade ao trabalho ||| Instabilidade econômica e restrições orçamentárias que impactam a continuidade de projetos e investimentos. ||| Instabilidade orçamentária e restrições de recursos públicos para capacitação de equipe. ||| Limitações de Recursos: Restrições orçamentárias podem afetar a implementação de melhorias que exijam investimentos em tecnologia ou infraestrutura ||| Limitações orçamentarias que possam restringir investimentos em tecnologia, capacitação e melhoria das ferramentas utilizadas. ||| Limitações orçamentárias para iniciativas de modernização. ||| Limitações orçamentárias que impactam investimentos em tecnologia e melhoria contínua. ||| Limitações orçamentárias. ||| Redução de repasses ||| Redução de repasses de verbas públicas devido a crises econômicas ou mudanças nas prioridades fiscais do Estado. ||| Redução de verbas públicas ||| Restrição de recursos (humanos e orçamentários) ||| Restrição de recursos orçamentários. ||| Restrições fiscais e limitações orçamentárias podem reduzir investimentos em tecnologia, capacitação e modernização administrativa. Isso impacta diretamente a capacidade do escritório de processos de implementar soluções mais robustas, como automação e digitalização, além de limitar a expansão de projetos estruturantes. ||| Restrições orçamentárias ||| Restrições orçamentárias, limitando investimentos em tecnologia e melhoria de processo ||| corte orçamentário ||| falta de patrocinios nos orgãos</t>
+          <t>A falta de recursos pode limitar ações de capacitação, tecnologia e melhoria de processos. ||| Conflito por recursos e atenção com outras áreas e programas do governo, que podem diluir o foco nas iniciativas do EPROC ||| Falta de investimento financeiro do governo do estado ||| Falta de recursos para dar continuidade ao trabalho ||| Instabilidade econômica e restrições orçamentárias que impactam a continuidade de projetos e investimentos. ||| Instabilidade orçamentária e restrições de recursos públicos para capacitação de equipe. ||| Limitações de Recursos: Restrições orçamentárias podem afetar a implementação de melhorias que exijam investimentos em tecnologia ou infraestrutura ||| Limitações orçamentarias que possam restringir investimentos em tecnologia, capacitação e melhoria das ferramentas utilizadas. ||| Limitações orçamentárias para iniciativas de modernização. ||| Limitações orçamentárias que impactam investimentos em tecnologia e melhoria contínua. ||| Limitações orçamentárias. ||| Redução de repasses ||| Redução de repasses de verbas públicas devido a crises econômicas ou mudanças nas prioridades fiscais do Estado. ||| Redução de verbas públicas ||| Restrição de recursos (humanos e orçamentários) ||| Restrição de recursos orçamentários. ||| Restrições fiscais e limitações orçamentárias podem reduzir investimentos em tecnologia, capacitação e modernização administrativa. Isso impacta diretamente a capacidade do escritório de processos de implementar soluções mais robustas, como automação e digitalização, além de limitar a expansão de projetos estruturantes. ||| Restrições orçamentárias ||| Restrições orçamentárias, limitando investimentos em tecnologia e melhoria de processo ||| corte orçamentário ||| falta de patrocinios nos orgãos</t>
         </is>
       </c>
     </row>
@@ -1521,18 +1479,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Não classificado (revisar manualmente)</t>
+          <t>Dependência de decisões e engajamento externo</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>7.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ameaça é qualquer condição que pode gerar riscos, instabilidade ou prejuízos, afetando o desempenho e a segurança de uma instituição. ||| Ameaça é um elemento que impõe desafios e pressões capazes de enfraquecer processos e comprometer resultados se não for devidamente enfrentado. ||| Ameaça é um fator que pode comprometer objetivos e resultados, exigindo atenção e respostas rápidas para reduzir seus impactos. ||| Baixa cultura de processos nos órgãos ||| Baixo conhecimento da importancia da gestão de processos ||| Crescimento tecnológico do mercado ||| Dependência crítica de tecnologia externa (CIASC) ||| Dependência de decisões de outros órgãos. ||| Dependência de fornecedores e sistemas externos, podendo gerar instabilidade ou indisponibilidade dos serviços. ||| Evolução acelerada de tecnologias sem o devido acompanhamento institucional, gerando defasagem operacional. ||| Falta de conhecimento sobre o assunto ||| Instabilidade de Infraestrutura: Indisponibilidade total ou temporária de sistemas de tecnologia pode paralisar o atendimento e a continuidade dos serviços públicos ||| Limitações de infraestrutura tecnológica ||| Limitações tecnológicas ou instabilidades nos sistemas utilizados, comprometendo o fluxo e o acompanhamento das demandas ||| Mudanças de diretrizes governamentais ou prioridades institucionais que impactam a continuidade das ações de mapeamento de processos ||| Mudanças na gestão estadual que podem alterar prioridades e descontinuar iniciativas ||| Vulnerabilidade cibernética, vários sistemas ||| dependência de decisões instâncias superioress ||| falta de cultura de Gestão de Processos nos órgão</t>
+          <t>A baixa participação dos órgãos pode dificultar a atuação do EPROC. ||| A dificuldade de engajamento de algumas unidades organizacionais pode comprometer a implementação e a sustentabilidade das melhorias propostas. ||| Baixa adesão ou priorização dos órgãos na formalização de demandas via eproc, dificultando a organização e o planejamento das atividades ||| Baixa priorização da gestão de processos frente a demandas urgentes ||| Baixo nível de priorização da gestão por processos pela alta gestão dos órgãos ||| Dependência de decisões de outros órgãos. ||| Dificuldade nos contatos ||| Falta de adesão entre os órgãos/secretarias ||| Falta de interesse dos órgãos ||| Resistência Cultural: Riscos de resistência organizacional e baixa adesão às mudanças propostas, o que pode manter práticas antigas e ineficientes ||| Sobrecarga das áreas, dificultando execução dos mapeamentos ||| dependência de decisões instâncias superioress</t>
         </is>
       </c>
     </row>
@@ -1542,18 +1500,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Baixo engajamento e adesão dos órgãos</t>
+          <t>Complexidade e qualidade das demandas</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>A baixa participação dos órgãos pode dificultar a atuação do EPROC. ||| A dificuldade de engajamento de algumas unidades organizacionais pode comprometer a implementação e a sustentabilidade das melhorias propostas. ||| A falta de engajamento da alta gestão pode enfraquecer as iniciativas de gestão por processos. ||| Baixa adesão ou priorização dos órgãos na formalização de demandas via eproc, dificultando a organização e o planejamento das atividades ||| Baixa priorização da gestão de processos frente a demandas urgentes ||| Baixo engajamento dos órgãos estaduais ||| Baixo engajamento dos órgãos na adoção da gestão por processos. ||| Baixo nível de priorização da gestão por processos pela alta gestão dos órgãos ||| Dificuldade nos contatos ||| Falta de adesão entre os órgãos/secretarias ||| Falta de interesse dos órgãos ||| Sobrecarga das áreas, dificultando execução dos mapeamentos</t>
+          <t>Aumento da complexidade das demandas da administração pública ||| Crescimento da demanda por perícias. ||| Critérios para definir o que realmente deverá ser cadastrado no Taiga e identificar o que é importante se modelado no Camunda. ||| Desinteresse ou falta de capacitação dos produtores culturais para operarem os novos sistemas digitais de inscrição. ||| Eventos climáticos adversos e instabilidades no setor agropecuário, impactando diretamente a demanda e a execução das políticas públicas. ||| Excesso ||| Fatores Climáticos Extremos ||| Qualidade dos dados encaminhados aos processos, retrabalhos e gargalos. ||| Quanto a elaboração da Cadeia de Valor pelo especialista do Nuproc é subjetiva. Toda Cadeia de Valor deveria ser realizada com a participação do Eproc, pois nesta fase será identificada a veracidade e abrangência do Inventário de Processos. ||| especialista sem boa comunicação ||| falta de flexibilidade do especialista</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Complexidade e qualidade das demandas</t>
+          <t>Dependência tecnológica e instabilidade de sistemas</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1574,7 +1532,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aumento da complexidade das demandas da administração pública ||| Crescimento da demanda por perícias. ||| Critérios para definir o que realmente deverá ser cadastrado no Taiga e identificar o que é importante se modelado no Camunda. ||| Desinteresse ou falta de capacitação dos produtores culturais para operarem os novos sistemas digitais de inscrição. ||| Eventos climáticos adversos e instabilidades no setor agropecuário, impactando diretamente a demanda e a execução das políticas públicas. ||| Excesso ||| Fatores Climáticos Extremos ||| Qualidade dos dados encaminhados aos processos, retrabalhos e gargalos. ||| Quanto a elaboração da Cadeia de Valor pelo especialista do Nuproc é subjetiva. Toda Cadeia de Valor deveria ser realizada com a participação do Eproc, pois nesta fase será identificada a veracidade e abrangência do Inventário de Processos. ||| especialista sem boa comunicação ||| falta de flexibilidade do especialista</t>
+          <t>A insuficiência de investimentos em soluções como inteligência artificial e automação limita a modernização dos processos e reduz o potencial de ganho de eficiência institucional. ||| Crescimento tecnológico do mercado ||| Dependência crítica de tecnologia externa (CIASC) ||| Dependência de fornecedores e sistemas externos, podendo gerar instabilidade ou indisponibilidade dos serviços. ||| Evolução acelerada de tecnologias sem o devido acompanhamento institucional, gerando defasagem operacional. ||| Instabilidade de Infraestrutura: Indisponibilidade total ou temporária de sistemas de tecnologia pode paralisar o atendimento e a continuidade dos serviços públicos ||| Limitações de infraestrutura tecnológica ||| Limitações tecnológicas ou instabilidades nos sistemas utilizados, comprometendo o fluxo e o acompanhamento das demandas ||| Obsolescência tecnológica do EPROC pode levar órgãos a adotar soluções isoladas para a Gestão de Processos ||| Tecnologias que prometem entregar soluções prontas ||| Vulnerabilidade cibernética, vários sistemas</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1542,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Resistência cultural à mudança</t>
+          <t>Rotatividade e perda de talentos</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1595,7 +1553,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>A resistência a mudanças pode atrasar a implementação de melhorias nos processos. ||| Baixa maturidade e cultura organizacional dos orgãos em Gestão de Processos ||| Cultura organizacional de alguns órgãos pode dificultar a implementação de melhorias e novas práticas ||| Cultura organizacional resistente a mudanças ||| Não aceitação das orientações ||| Resistencia  á   mudanças por parte de alguns órgãos ou equipes, dificultando a implementação das melhorias propostas. ||| Resistência Cultural: Riscos de resistência organizacional e baixa adesão às mudanças propostas, o que pode manter práticas antigas e ineficientes ||| Resistência cultural à mudança em áreas demandantes, dificultando adoção de novos fluxos e metodologias. Rotatividade de gestores e servidores-chave, comprometendo continuidade e alinhamento de projetos estratégicos. ||| Resistência cultural à mudança nos órgãos ||| Resistência à mudança nos órgãos</t>
+          <t>Alta rotatividade de pessoal. ||| Cargos com bastante rotatividade ||| Dificuldade m manter profissionais acima da média e que detém o  conhecimento necessário para um  trabalho robusto e com máxima qualidade ||| Diminuição da quantidade de colaboradores, que pode se dar por concorrência de mercado ou o fim de vínculo com os especialistas. ||| Evasão de Talentos ||| Formato de contratação ||| Mudança de especialistas nos órgãos (buscar por transição mais estruturada e preservação do histórico) ||| Oportunidades de trabalho mais atrativas ||| Perda de conhecimento com a saída de servidores e colaboradores ||| rotatividade de bolsistas</t>
         </is>
       </c>
     </row>
@@ -1605,18 +1563,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rotatividade e perda de talentos</t>
+          <t>Baixo reconhecimento institucional do EPROC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alta rotatividade de pessoal. ||| Cargos com bastante rotatividade ||| Dificuldade m manter profissionais acima da média e que detém o  conhecimento necessário para um  trabalho robusto e com máxima qualidade ||| Diminuição da quantidade de colaboradores, que pode se dar por concorrência de mercado ou o fim de vínculo com os especialistas. ||| Evasão de Talentos ||| Formato de contratação ||| Mudança de especialistas nos órgãos (buscar por transição mais estruturada e preservação do histórico) ||| Oportunidades de trabalho mais atrativas ||| Perda de conhecimento com a saída de servidores e colaboradores ||| rotatividade de bolsistas</t>
+          <t>Baixa percepção de valor com relação ao Eproc, por órgãos do governo de SC que estão mais avançados em gestão por processos (que tem expectativa para além da representação dos diagramas e ITs) ||| Descredibilização interna ||| Expectativa elevada sobre a secretaria sem contrapartida estrutural, gerando cobrança superior à sua capacidade operacional instalada ||| Falta de mensuração clara de impacto ||| Importancia e papel do Eproc não ser devidamente compreendida por seus stakeholders ||| Incompreensão ||| Retornos sem "valor" para o nosso trabalho ||| baixo reconhecimento institucional ||| desestimularão</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1584,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Baixo reconhecimento institucional do EPROC</t>
+          <t>Instabilidade normativa e complexidade regulatória</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1637,7 +1595,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baixa percepção de valor com relação ao Eproc, por órgãos do governo de SC que estão mais avançados em gestão por processos (que tem expectativa para além da representação dos diagramas e ITs) ||| Descredibilização interna ||| Expectativa elevada sobre a secretaria sem contrapartida estrutural, gerando cobrança superior à sua capacidade operacional instalada ||| Falta de mensuração clara de impacto ||| Importancia e papel do Eproc não ser devidamente compreendida por seus stakeholders ||| Incompreensão ||| Retornos sem "valor" para o nosso trabalho ||| baixo reconhecimento institucional ||| desestimularão</t>
+          <t>A rigidez normativa, somada à complexidade de legislações como a Lei de Licitações (Lei nº 14.133/2021) e exigências da Lei Geral de Proteção de Dados (LGPD), pode tornar mais lenta a implementação de melhorias e inovações. Processos de contratação demorados, necessidade de conformidade e excesso de formalismo podem dificultar a agilidade necessária para promover mudanças efetivas. ||| Alterações frequentes nas legislações de fomento cultural que podem invalidar processos de editais em andamento. ||| Alterações legislativas ou normativas que exijam retrabalho e adaptação rápida de processos mapeados. Concorrência por atenção e recursos internos com outras prioridades e demandas da gestão. ||| Complexidade Burocrática: Excesso de normativas legais ||| Incertezas Regulatórias: A alta complexidade normativa e mudanças frequentes na legislação podem gerar insegurança jurídica ou exigir revisões constantes nos processos mapeados ||| Mudanças Regulatórias: Alterações frequentes na legislação ou estratégias governamentais podem exigir revisões constantes no portfólio de processos ||| Mudanças frequentes na legislação e normativas, impactando a estabilidade e padronização dos processos. ||| Necessidade de extremo cuidado com dados que possam ter relação com a LGPD. ||| reconhecimento, pela alta gestão, da importância do núcleo de processos, com a formalização por meio de normativas e definição de um gestor responsável (patrocinador) para garantir a governança e o suporte aos especialistas nos órgãos.</t>
         </is>
       </c>
     </row>
@@ -1647,18 +1605,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Instabilidade normativa e complexidade regulatória</t>
+          <t>Resistência cultural à mudança</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A rigidez normativa, somada à complexidade de legislações como a Lei de Licitações (Lei nº 14.133/2021) e exigências da Lei Geral de Proteção de Dados (LGPD), pode tornar mais lenta a implementação de melhorias e inovações. Processos de contratação demorados, necessidade de conformidade e excesso de formalismo podem dificultar a agilidade necessária para promover mudanças efetivas. ||| Alterações frequentes nas legislações de fomento cultural que podem invalidar processos de editais em andamento. ||| Alterações legislativas ou normativas que exijam retrabalho e adaptação rápida de processos mapeados. Concorrência por atenção e recursos internos com outras prioridades e demandas da gestão. ||| Complexidade Burocrática: Excesso de normativas legais ||| Incertezas Regulatórias: A alta complexidade normativa e mudanças frequentes na legislação podem gerar insegurança jurídica ou exigir revisões constantes nos processos mapeados ||| Mudanças Regulatórias: Alterações frequentes na legislação ou estratégias governamentais podem exigir revisões constantes no portfólio de processos ||| Mudanças frequentes na legislação e normativas, impactando a estabilidade e padronização dos processos. ||| Necessidade de extremo cuidado com dados que possam ter relação com a LGPD. ||| reconhecimento, pela alta gestão, da importância do núcleo de processos, com a formalização por meio de normativas e definição de um gestor responsável (patrocinador) para garantir a governança e o suporte aos especialistas nos órgãos.</t>
+          <t>A resistência a mudanças pode atrasar a implementação de melhorias nos processos. ||| Cultura organizacional de alguns órgãos pode dificultar a implementação de melhorias e novas práticas ||| Cultura organizacional resistente a mudanças ||| Não aceitação das orientações ||| Resistencia  á   mudanças por parte de alguns órgãos ou equipes, dificultando a implementação das melhorias propostas. ||| Resistência cultural à mudança em áreas demandantes, dificultando adoção de novos fluxos e metodologias. Rotatividade de gestores e servidores-chave, comprometendo continuidade e alinhamento de projetos estratégicos. ||| Resistência cultural à mudança nos órgãos ||| Resistência à mudança nos órgãos</t>
         </is>
       </c>
     </row>
@@ -1672,14 +1630,14 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Consultorias de processos ||| Existência de especialistas em processos nos órgãos sem vinculação obrigatória à metodologia do eproc, gerando a necessidade de alinhamento institucional para padronização das práticas e integração das iniciativas. ||| Interferências de órgãos de controle ||| Obsolescência tecnológica do EPROC pode levar órgãos a adotar soluções isoladas para a Gestão de Processos ||| Outros editais concorrentes ||| Tecnologias que prometem entregar soluções prontas ||| Uso indiscriminado de IA pelos especialistas dos Nuproc’s na execução de seus trabalhos ||| outros editais similares</t>
+          <t>Consultorias de processos ||| Existência de especialistas em processos nos órgãos sem vinculação obrigatória à metodologia do eproc, gerando a necessidade de alinhamento institucional para padronização das práticas e integração das iniciativas. ||| Interferências de órgãos de controle ||| Outros editais concorrentes ||| Uso indiscriminado de IA pelos especialistas dos Nuproc’s na execução de seus trabalhos ||| outros editais similares</t>
         </is>
       </c>
     </row>
@@ -1689,18 +1647,81 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Baixa maturidade e cultura de processos nos órgãos</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Baixa cultura de processos nos órgãos ||| Baixa maturidade e cultura organizacional dos orgãos em Gestão de Processos ||| Baixo conhecimento da importancia da gestão de processos ||| Falta de conhecimento sobre o assunto ||| falta de cultura de Gestão de Processos nos órgão</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Desafios institucionais e percepção de ameaça</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ameaça é qualquer condição que pode gerar riscos, instabilidade ou prejuízos, afetando o desempenho e a segurança de uma instituição. ||| Ameaça é um elemento que impõe desafios e pressões capazes de enfraquecer processos e comprometer resultados se não for devidamente enfrentado. ||| Ameaça é um fator que pode comprometer objetivos e resultados, exigindo atenção e respostas rápidas para reduzir seus impactos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Déficit de servidores efetivos e de carreira</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>A carência de servidores de carreira para a sustentação dos processos coloca em risco a integridade e a perenidade do conhecimento acumulado. ||| Falta de concurso público específico para Fesporte ||| Poucos servidores efetivos na SEPLAN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Não classificado (revisar manualmente)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A falta de engajamento da alta gestão pode enfraquecer as iniciativas de gestão por processos. ||| Baixo engajamento dos órgãos estaduais ||| Baixo engajamento dos órgãos na adoção da gestão por processos.</t>
         </is>
       </c>
     </row>
@@ -1750,10 +1771,10 @@
         <v>162</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1766,10 +1787,10 @@
         <v>153</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1782,10 +1803,10 @@
         <v>151</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1798,10 +1819,10 @@
         <v>152</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
